--- a/data/trans_dic/P56$amigo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 18,54</t>
+          <t>2,28; 17,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,48</t>
+          <t>1,1; 6,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>0,68; 6,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,34</t>
+          <t>2,22; 6,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,2</t>
+          <t>0,81; 7,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,04</t>
+          <t>0,83; 4,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,4</t>
+          <t>0,49; 4,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,4</t>
+          <t>1,91; 5,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 21,31</t>
+          <t>1,76; 21,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,99</t>
+          <t>0,82; 9,1</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,4</t>
+          <t>0,0; 51,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,15</t>
+          <t>0,0; 40,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,15</t>
+          <t>0,0; 36,15</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 16,78</t>
+          <t>2,1; 15,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,66</t>
+          <t>1,55; 8,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,87</t>
+          <t>1,03; 5,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,57</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,89</t>
+          <t>2,26; 5,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,32</t>
+          <t>1,39; 8,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,02</t>
+          <t>0,74; 4,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,84</t>
+          <t>0,4; 3,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,39</t>
+          <t>2,39; 5,4</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1006; 8182</t>
+          <t>1007; 7849</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2218</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3829</t>
+          <t>0; 3647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6397</t>
+          <t>0; 5535</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2088; 12050</t>
+          <t>2054; 11241</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9057</t>
+          <t>972; 9128</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4521; 12719</t>
+          <t>4446; 12617</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1035; 10460</t>
+          <t>1037; 9967</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2097; 12807</t>
+          <t>2121; 12332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>984; 8780</t>
+          <t>975; 8980</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5227; 14502</t>
+          <t>5138; 13465</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1268</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1622</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>486; 5775</t>
+          <t>477; 5914</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1788</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1845</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2297</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2863</t>
+          <t>0; 2738</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1712</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2114</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>787; 6914</t>
+          <t>570; 6298</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3523</t>
+          <t>0; 3361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2403</t>
+          <t>0; 2626</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4808</t>
+          <t>0; 4679</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1008; 8102</t>
+          <t>1013; 7266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1545; 8793</t>
+          <t>1574; 8626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7043</t>
+          <t>0; 6632</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2076; 11875</t>
+          <t>2074; 12048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>974; 9572</t>
+          <t>973; 8504</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5140; 14684</t>
+          <t>5621; 14672</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1926; 10378</t>
+          <t>1978; 11567</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2095; 11275</t>
+          <t>2082; 12142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>996; 9353</t>
+          <t>978; 9233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8041; 18884</t>
+          <t>8378; 18936</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$amigo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 17,78</t>
+          <t>2,25; 16,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,04</t>
+          <t>1,11; 5,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,39</t>
+          <t>0,68; 5,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,29</t>
+          <t>2,1; 6,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,81</t>
+          <t>0,81; 7,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,85</t>
+          <t>0,84; 4,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,5</t>
+          <t>0,47; 4,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,02</t>
+          <t>1,9; 5,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 21,82</t>
+          <t>0,0; 20,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,1</t>
+          <t>0,9; 8,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,9</t>
+          <t>0,0; 47,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,6</t>
+          <t>0,0; 32,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,15</t>
+          <t>0,0; 28,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,05</t>
+          <t>2,1; 15,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,5</t>
+          <t>1,51; 7,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,96</t>
+          <t>1,04; 5,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,56; 4,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,89</t>
+          <t>2,03; 5,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,16</t>
+          <t>1,37; 7,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,33</t>
+          <t>0,42; 4,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,79</t>
+          <t>0,4; 3,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,4</t>
+          <t>2,41; 5,42</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9385</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1007; 7849</t>
+          <t>992; 7131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1519,47 +1519,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3647</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5535</t>
+          <t>0; 5615</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2054; 11241</t>
+          <t>2057; 11098</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>972; 9128</t>
+          <t>972; 8334</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4446; 12617</t>
+          <t>4556; 13712</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1037; 9967</t>
+          <t>1034; 9546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2121; 12332</t>
+          <t>2135; 11992</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>975; 8980</t>
+          <t>941; 8879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5138; 13465</t>
+          <t>5496; 15176</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2660</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>477; 5914</t>
+          <t>0; 5817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2738</t>
+          <t>0; 2598</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>570; 6298</t>
+          <t>690; 6744</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>645</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1571</t>
         </is>
       </c>
     </row>
@@ -1935,34 +1935,34 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 3402</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0; 3361</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>0; 3361</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2626</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3361</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4679</t>
+          <t>0; 4407</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13615</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1013; 7266</t>
+          <t>1012; 7720</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2143,47 +2143,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1574; 8626</t>
+          <t>1629; 8607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6763</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2074; 12048</t>
+          <t>2093; 11754</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>973; 8504</t>
+          <t>965; 8435</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5621; 14672</t>
+          <t>5539; 14890</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1978; 11567</t>
+          <t>1937; 11320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2082; 12142</t>
+          <t>1185; 11914</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978; 9233</t>
+          <t>977; 9130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8378; 18936</t>
+          <t>9174; 20687</t>
         </is>
       </c>
     </row>
